--- a/trip/trip-template.xlsx
+++ b/trip/trip-template.xlsx
@@ -195,7 +195,9 @@
       <text>
         <t>아래에 장소/체험/식당 카드를 한 줄에 하나씩 적습니다.
 종류: 체험 / 먹기 / 쇼핑 / 숙소
-위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.</t>
+위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.
+체크인/체크아웃: 숙소만 · 출발/도착 시각과 도착위도/경도: 교통만 씁니다.
+숙소·교통은 시간(분)을 비워도 됩니다.</t>
       </text>
     </comment>
   </commentList>
@@ -212,7 +214,9 @@
       <text>
         <t>아래에 장소/체험/식당 카드를 한 줄에 하나씩 적습니다.
 종류: 체험 / 먹기 / 쇼핑 / 숙소
-위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.</t>
+위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.
+체크인/체크아웃: 숙소만 · 출발/도착 시각과 도착위도/경도: 교통만 씁니다.
+숙소·교통은 시간(분)을 비워도 됩니다.</t>
       </text>
     </comment>
   </commentList>
@@ -508,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -517,7 +521,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,6 +617,36 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>체크인</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>체크아웃</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>출발시각</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>도착시각</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>도착위도</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>도착경도</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -638,6 +678,12 @@
           <t>맨발로 물속을 걷는 빛의 미술관</t>
         </is>
       </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -669,6 +715,12 @@
           <t>도쿄에서 제일 높은 전망대</t>
         </is>
       </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -700,6 +752,12 @@
           <t>큰 빨간 등이 있는 오래된 절</t>
         </is>
       </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -731,6 +789,12 @@
           <t>판다를 볼 수 있는 동물원</t>
         </is>
       </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -762,6 +826,12 @@
           <t>1인 좌석에서 먹는 돈코츠 라멘</t>
         </is>
       </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -793,6 +863,12 @@
           <t>레일 위로 초밥이 지나가요</t>
         </is>
       </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -824,6 +900,12 @@
           <t>포켓몬 굿즈가 가득한 가게</t>
         </is>
       </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -855,6 +937,12 @@
           <t>지하에 캐릭터 가게가 쭉</t>
         </is>
       </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -867,9 +955,7 @@
           <t>숙소</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>60</v>
-      </c>
+      <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
         <v>35.711</v>
@@ -882,15 +968,67 @@
           <t>짐 놓고 쉬는 우리 집</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>나리타 익스프레스</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>교통</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>₩₩</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>35.772</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>140.3929</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>나리타공항→도쿄역 · JR 개찰 B1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>35.6812</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>139.7671</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -900,6 +1038,12 @@
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -909,6 +1053,12 @@
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -918,6 +1068,12 @@
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -927,6 +1083,12 @@
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -936,6 +1098,12 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -945,6 +1113,12 @@
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -954,6 +1128,12 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -963,6 +1143,12 @@
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -972,6 +1158,12 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -981,6 +1173,12 @@
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -990,6 +1188,12 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -999,6 +1203,12 @@
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1008,6 +1218,12 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1017,6 +1233,12 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1026,6 +1248,12 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1035,6 +1263,12 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1044,6 +1278,12 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1053,6 +1293,12 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1062,6 +1308,12 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1071,6 +1323,12 @@
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1080,6 +1338,12 @@
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1089,6 +1353,12 @@
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1098,6 +1368,12 @@
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1107,6 +1383,12 @@
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1116,6 +1398,12 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1125,6 +1413,12 @@
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1134,6 +1428,12 @@
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1143,6 +1443,12 @@
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1152,11 +1458,32 @@
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B6:B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 숙소 중 하나" type="list">
-      <formula1>"체험,먹기,쇼핑,숙소"</formula1>
+    <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 숙소 중 하나" type="list">
+      <formula1>"체험,먹기,쇼핑,교통,숙소"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1170,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1179,7 +1506,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1269,6 +1602,36 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>체크인</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>체크아웃</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>출발시각</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>도착시각</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>도착위도</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>도착경도</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1300,6 +1663,12 @@
           <t>큰 수족관 — 이 줄은 지우고 쓰세요</t>
         </is>
       </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1309,6 +1678,12 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1318,6 +1693,12 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1327,6 +1708,12 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1336,6 +1723,12 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1345,6 +1738,12 @@
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1354,6 +1753,12 @@
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1363,6 +1768,12 @@
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1372,6 +1783,12 @@
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1381,6 +1798,12 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1390,6 +1813,12 @@
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1399,6 +1828,12 @@
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1408,6 +1843,12 @@
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1417,6 +1858,12 @@
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1426,6 +1873,12 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1435,6 +1888,12 @@
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1444,6 +1903,12 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1453,6 +1918,12 @@
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1462,6 +1933,12 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1471,6 +1948,12 @@
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1480,6 +1963,12 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1489,6 +1978,12 @@
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1498,6 +1993,12 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1507,6 +2008,12 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1516,6 +2023,12 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1525,6 +2038,12 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1534,6 +2053,12 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1543,6 +2068,12 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1552,6 +2083,12 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1561,6 +2098,12 @@
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1570,11 +2113,17 @@
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B6:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 숙소 중 하나" type="list">
-      <formula1>"체험,먹기,쇼핑,숙소"</formula1>
+      <formula1>"체험,먹기,쇼핑,교통,숙소"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trip/trip-template.xlsx
+++ b/trip/trip-template.xlsx
@@ -48,7 +48,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002B2B33"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0035695B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003D5A82"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,13 +107,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,11 +209,20 @@
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>아래에 장소/체험/식당 카드를 한 줄에 하나씩 적습니다.
-종류: 체험 / 먹기 / 쇼핑 / 숙소
-위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.
-체크인/체크아웃: 숙소만 · 출발/도착 시각과 도착위도/경도: 교통만 씁니다.
+        <t>아래에 카드를 한 줄에 하나씩 적습니다.
+종류: 체험 / 먹기 / 쇼핑 / 교통 / 숙소
+위치: 구글 지도 '긴 주소'를 지도링크 칸에 붙여넣거나(그러면 위도/경도는 비워도 됨),
+  장소를 길게 눌러 나온 위도/경도 숫자를 직접 넣습니다.
+  ⚠️ 폰 공유용 짧은 링크(maps.app.goo.gl)에는 좌표가 없어요 — 한 번 열어 긴 주소를 복사하세요.
+할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
+초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
 숙소·교통은 시간(분)을 비워도 됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>구글 지도에서 장소 페이지를 열고 브라우저 주소창의 긴 주소를 복사해 붙여넣으세요.
+이 칸을 채우면 위도/경도는 비워도 됩니다.</t>
       </text>
     </comment>
   </commentList>
@@ -212,11 +237,20 @@
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>아래에 장소/체험/식당 카드를 한 줄에 하나씩 적습니다.
-종류: 체험 / 먹기 / 쇼핑 / 숙소
-위도·경도: 구글 지도에서 장소를 길게 누르면 나옵니다.
-체크인/체크아웃: 숙소만 · 출발/도착 시각과 도착위도/경도: 교통만 씁니다.
+        <t>아래에 카드를 한 줄에 하나씩 적습니다.
+종류: 체험 / 먹기 / 쇼핑 / 교통 / 숙소
+위치: 구글 지도 '긴 주소'를 지도링크 칸에 붙여넣거나(그러면 위도/경도는 비워도 됨),
+  장소를 길게 눌러 나온 위도/경도 숫자를 직접 넣습니다.
+  ⚠️ 폰 공유용 짧은 링크(maps.app.goo.gl)에는 좌표가 없어요 — 한 번 열어 긴 주소를 복사하세요.
+할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
+초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
 숙소·교통은 시간(분)을 비워도 됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>구글 지도에서 장소 페이지를 열고 브라우저 주소창의 긴 주소를 복사해 붙여넣으세요.
+이 칸을 채우면 위도/경도는 비워도 됩니다.</t>
       </text>
     </comment>
   </commentList>
@@ -512,22 +546,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,45 +641,60 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>지도링크</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>위도</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>경도</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>할일메모</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>체크인</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>체크아웃</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>출발시각</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>도착시각</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>도착지도링크</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>도착위도</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>도착경도</t>
         </is>
@@ -659,7 +711,7 @@
           <t>체험</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>120</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -667,23 +719,30 @@
           <t>₩₩₩</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>35.6493</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>139.7891</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>맨발로 물속을 걷는 빛의 미술관</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/teamLab+Planets/@35.6493003,139.7891321,17z/data=!3m1!4b1!4m6!3m5!1s0x0:0x0!8m2!3d35.6493003!4d139.7891321</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>예약 시간 지키기; 갈아입을 양말 챙기기</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -696,7 +755,7 @@
           <t>체험</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="8" t="n">
         <v>90</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -704,23 +763,26 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>도쿄에서 제일 높은 전망대</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="n">
         <v>35.7101</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>139.8107</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>도쿄에서 제일 높은 전망대</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -733,7 +795,7 @@
           <t>체험</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="8" t="n">
         <v>60</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -741,23 +803,30 @@
           <t>무료</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>큰 빨간 등이 있는 오래된 절</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="n">
         <v>35.7148</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>139.7967</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>큰 빨간 등이 있는 오래된 절</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>오미쿠지 뽑아 보기</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -770,7 +839,7 @@
           <t>체험</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="8" t="n">
         <v>150</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -778,23 +847,26 @@
           <t>₩</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>판다를 볼 수 있는 동물원</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="n">
         <v>35.7163</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>139.7714</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>판다를 볼 수 있는 동물원</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -807,7 +879,7 @@
           <t>먹기</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="8" t="n">
         <v>45</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -815,23 +887,26 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1인 좌석에서 먹는 돈코츠 라멘</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="n">
         <v>35.6595</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>139.7005</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1인 좌석에서 먹는 돈코츠 라멘</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -844,7 +919,7 @@
           <t>먹기</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="8" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -852,23 +927,26 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>레일 위로 초밥이 지나가요</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="n">
         <v>35.698</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>139.7745</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>레일 위로 초밥이 지나가요</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -881,7 +959,7 @@
           <t>쇼핑</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>60</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -889,23 +967,30 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>포켓몬 굿즈가 가득한 가게</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="n">
         <v>35.729</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>139.719</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>포켓몬 굿즈가 가득한 가게</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>용돈 한도 정하고 가기</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -918,7 +1003,7 @@
           <t>쇼핑</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="8" t="n">
         <v>50</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -926,23 +1011,26 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>지하에 캐릭터 가게가 쭉</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="n">
         <v>35.6812</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>139.7671</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>지하에 캐릭터 가게가 쭉</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -955,33 +1043,40 @@
           <t>숙소</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>짐 놓고 쉬는 우리 집</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="n">
         <v>35.711</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>139.777</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>짐 놓고 쉬는 우리 집</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>여권은 프런트 금고에</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -994,46 +1089,53 @@
           <t>교통</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>나리타공항→도쿄역 · JR 개찰 B1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="n">
         <v>35.772</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>140.3929</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>나리타공항→도쿄역 · JR 개찰 B1</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>지정석 표 미리 받기</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="n">
         <v>35.6812</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>139.7671</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="8" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
@@ -1044,11 +1146,14 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
@@ -1059,11 +1164,14 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
@@ -1074,11 +1182,14 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
@@ -1089,11 +1200,14 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
@@ -1104,11 +1218,14 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="8" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
@@ -1119,11 +1236,14 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="n"/>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="8" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
@@ -1134,11 +1254,14 @@
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
@@ -1149,11 +1272,14 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="2" t="n"/>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="8" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
@@ -1164,11 +1290,14 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n"/>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="8" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
@@ -1179,11 +1308,14 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="n"/>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="8" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1194,11 +1326,14 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n"/>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="8" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
@@ -1209,11 +1344,14 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="8" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
@@ -1224,11 +1362,14 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="8" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
@@ -1239,11 +1380,14 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="2" t="n"/>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" s="8" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
@@ -1254,11 +1398,14 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="8" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
@@ -1269,11 +1416,14 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="2" t="n"/>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
@@ -1284,11 +1434,14 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="n"/>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="8" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
@@ -1299,11 +1452,14 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="2" t="n"/>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
@@ -1314,11 +1470,14 @@
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="n"/>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="8" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
@@ -1329,11 +1488,14 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="n"/>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="8" t="n"/>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
@@ -1344,11 +1506,14 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="n"/>
-      <c r="C37" s="6" t="n"/>
+      <c r="C37" s="8" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
@@ -1359,11 +1524,14 @@
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
       <c r="B38" s="2" t="n"/>
-      <c r="C38" s="6" t="n"/>
+      <c r="C38" s="8" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
@@ -1374,11 +1542,14 @@
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="2" t="n"/>
-      <c r="C39" s="6" t="n"/>
+      <c r="C39" s="8" t="n"/>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
@@ -1389,11 +1560,14 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="2" t="n"/>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="8" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
@@ -1404,11 +1578,14 @@
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="2" t="n"/>
-      <c r="C41" s="6" t="n"/>
+      <c r="C41" s="8" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
@@ -1419,11 +1596,14 @@
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="2" t="n"/>
-      <c r="C42" s="6" t="n"/>
+      <c r="C42" s="8" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
@@ -1434,11 +1614,14 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="n"/>
-      <c r="C43" s="6" t="n"/>
+      <c r="C43" s="8" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
@@ -1449,11 +1632,14 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="2" t="n"/>
-      <c r="C44" s="6" t="n"/>
+      <c r="C44" s="8" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -1464,11 +1650,14 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="n"/>
-      <c r="C45" s="6" t="n"/>
+      <c r="C45" s="8" t="n"/>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n"/>
@@ -1479,10 +1668,13 @@
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 숙소 중 하나" type="list">
+    <dataValidation sqref="B6:B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 교통 / 숙소 중 하나" type="list">
       <formula1>"체험,먹기,쇼핑,교통,숙소"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1497,22 +1689,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1589,45 +1784,60 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>지도링크</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>위도</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>경도</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>할일메모</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>체크인</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>체크아웃</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>출발시각</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>도착시각</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>도착지도링크</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>도착위도</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>도착경도</t>
         </is>
@@ -1644,7 +1854,7 @@
           <t>체험</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>90</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1652,28 +1862,35 @@
           <t>₩₩</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>큰 수족관 — 이 줄은 지우고 쓰세요</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n">
         <v>33.4317</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>126.9276</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>큰 수족관 — 이 줄은 지우고 쓰세요</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>터치풀 시간 확인</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="8" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1684,11 +1901,14 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="8" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
@@ -1699,11 +1919,14 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="8" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
@@ -1714,11 +1937,14 @@
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
@@ -1729,11 +1955,14 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="8" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
@@ -1744,11 +1973,14 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
@@ -1759,11 +1991,14 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="8" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
@@ -1774,11 +2009,14 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
@@ -1789,11 +2027,14 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="n"/>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="8" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
@@ -1804,11 +2045,14 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="8" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
@@ -1819,11 +2063,14 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
@@ -1834,11 +2081,14 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
@@ -1849,11 +2099,14 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
@@ -1864,11 +2117,14 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
@@ -1879,11 +2135,14 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="8" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
@@ -1894,11 +2153,14 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="n"/>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="8" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
@@ -1909,11 +2171,14 @@
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
@@ -1924,11 +2189,14 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="2" t="n"/>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="8" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
@@ -1939,11 +2207,14 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n"/>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="8" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
@@ -1954,11 +2225,14 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="n"/>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="8" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1969,11 +2243,14 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n"/>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="8" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
@@ -1984,11 +2261,14 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="8" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
@@ -1999,11 +2279,14 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="8" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
@@ -2014,11 +2297,14 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="2" t="n"/>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" s="8" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
@@ -2029,11 +2315,14 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="8" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
@@ -2044,11 +2333,14 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="2" t="n"/>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
@@ -2059,11 +2351,14 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="n"/>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="8" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
@@ -2074,11 +2369,14 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="2" t="n"/>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
@@ -2089,11 +2387,14 @@
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="n"/>
-      <c r="C35" s="6" t="n"/>
+      <c r="C35" s="8" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
@@ -2104,11 +2405,14 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="n"/>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="8" t="n"/>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
@@ -2119,10 +2423,13 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B6:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 숙소 중 하나" type="list">
+    <dataValidation sqref="B6:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="종류" prompt="체험 / 먹기 / 쇼핑 / 교통 / 숙소 중 하나" type="list">
       <formula1>"체험,먹기,쇼핑,교통,숙소"</formula1>
     </dataValidation>
   </dataValidations>

--- a/trip/trip-template.xlsx
+++ b/trip/trip-template.xlsx
@@ -216,7 +216,8 @@
   ⚠️ 폰 공유용 짧은 링크(maps.app.goo.gl)에는 좌표가 없어요 — 한 번 열어 긴 주소를 복사하세요.
 할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
 초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
-숙소·교통은 시간(분)을 비워도 됩니다.</t>
+숙소·교통은 시간(분)을 비워도 됩니다.
+예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
@@ -244,7 +245,8 @@
   ⚠️ 폰 공유용 짧은 링크(maps.app.goo.gl)에는 좌표가 없어요 — 한 번 열어 긴 주소를 복사하세요.
 할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
 초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
-숙소·교통은 시간(분)을 비워도 됩니다.</t>
+숙소·교통은 시간(분)을 비워도 됩니다.
+예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
@@ -546,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -565,6 +567,7 @@
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,6 +702,11 @@
           <t>도착경도</t>
         </is>
       </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>예약시각</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -736,13 +744,18 @@
           <t>예약 시간 지키기; 갈아입을 양말 챙기기</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -783,6 +796,7 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -827,6 +841,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -867,6 +882,7 @@
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -907,6 +923,7 @@
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -947,6 +964,7 @@
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -991,6 +1009,7 @@
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1031,6 +1050,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1077,6 +1097,7 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1131,6 +1152,7 @@
       <c r="P15" s="2" t="n">
         <v>139.7671</v>
       </c>
+      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1149,6 +1171,7 @@
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1167,6 +1190,7 @@
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1185,6 +1209,7 @@
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1203,6 +1228,7 @@
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1221,6 +1247,7 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1239,6 +1266,7 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1257,6 +1285,7 @@
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1275,6 +1304,7 @@
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1293,6 +1323,7 @@
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1311,6 +1342,7 @@
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1329,6 +1361,7 @@
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1347,6 +1380,7 @@
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1365,6 +1399,7 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1383,6 +1418,7 @@
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1401,6 +1437,7 @@
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1419,6 +1456,7 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1437,6 +1475,7 @@
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1455,6 +1494,7 @@
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1473,6 +1513,7 @@
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1491,6 +1532,7 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1509,6 +1551,7 @@
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1527,6 +1570,7 @@
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1545,6 +1589,7 @@
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1563,6 +1608,7 @@
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1581,6 +1627,7 @@
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1599,6 +1646,7 @@
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1617,6 +1665,7 @@
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1635,6 +1684,7 @@
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1653,6 +1703,7 @@
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1671,6 +1722,7 @@
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1689,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1708,6 +1760,7 @@
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1840,6 +1893,11 @@
       <c r="P5" s="7" t="inlineStr">
         <is>
           <t>도착경도</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>예약시각</t>
         </is>
       </c>
     </row>
@@ -1886,6 +1944,7 @@
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1904,6 +1963,7 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1922,6 +1982,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1940,6 +2001,7 @@
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1958,6 +2020,7 @@
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1976,6 +2039,7 @@
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1994,6 +2058,7 @@
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -2012,6 +2077,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -2030,6 +2096,7 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -2048,6 +2115,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -2066,6 +2134,7 @@
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -2084,6 +2153,7 @@
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -2102,6 +2172,7 @@
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2120,6 +2191,7 @@
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2138,6 +2210,7 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2156,6 +2229,7 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2174,6 +2248,7 @@
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2192,6 +2267,7 @@
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2210,6 +2286,7 @@
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2228,6 +2305,7 @@
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2246,6 +2324,7 @@
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2264,6 +2343,7 @@
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2282,6 +2362,7 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2300,6 +2381,7 @@
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2318,6 +2400,7 @@
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2336,6 +2419,7 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2354,6 +2438,7 @@
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2372,6 +2457,7 @@
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2390,6 +2476,7 @@
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2408,6 +2495,7 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2426,6 +2514,7 @@
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/trip/trip-template.xlsx
+++ b/trip/trip-template.xlsx
@@ -217,7 +217,8 @@
 할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
 초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
 숙소·교통은 시간(분)을 비워도 됩니다.
-예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.</t>
+예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.
+사이트: 공식 홈페이지·예약 페이지 주소 — 앱의 🔗 버튼으로 열립니다.</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
@@ -246,7 +247,8 @@
 할일메모: '예약 확인; 우산 챙기기'처럼 ;로 구분 — 일정에 놓을 때 체크리스트로 들어갑니다.
 초록 열(체크인/체크아웃)은 숙소만, 파란 열(출발/도착)은 교통만 씁니다.
 숙소·교통은 시간(분)을 비워도 됩니다.
-예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.</t>
+예약시각: 입장·공연 예약이 있는 카드만 — 일정에 놓으면 ⏰ 예약 시각이 됩니다.
+사이트: 공식 홈페이지·예약 페이지 주소 — 앱의 🔗 버튼으로 열립니다.</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
@@ -548,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -568,6 +570,7 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,6 +708,11 @@
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>예약시각</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>사이트</t>
         </is>
       </c>
     </row>
@@ -754,6 +762,11 @@
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.teamlab.art/e/planets/</t>
         </is>
       </c>
     </row>
@@ -797,6 +810,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -842,6 +856,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -883,6 +898,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -924,6 +940,7 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -965,6 +982,7 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1010,6 +1028,7 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1051,6 +1070,7 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1098,6 +1118,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1153,6 +1174,7 @@
         <v>139.7671</v>
       </c>
       <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1172,6 +1194,7 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1191,6 +1214,7 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1210,6 +1234,7 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1229,6 +1254,7 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1248,6 +1274,7 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1267,6 +1294,7 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1286,6 +1314,7 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1305,6 +1334,7 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1324,6 +1354,7 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1343,6 +1374,7 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1362,6 +1394,7 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1381,6 +1414,7 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1400,6 +1434,7 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1419,6 +1454,7 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1438,6 +1474,7 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1457,6 +1494,7 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1476,6 +1514,7 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1495,6 +1534,7 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1514,6 +1554,7 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1533,6 +1574,7 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1552,6 +1594,7 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1571,6 +1614,7 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1590,6 +1634,7 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1609,6 +1654,7 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1628,6 +1674,7 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1647,6 +1694,7 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1666,6 +1714,7 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1685,6 +1734,7 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1704,6 +1754,7 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1723,6 +1774,7 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1741,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1813,7 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1898,6 +1951,11 @@
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>예약시각</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>사이트</t>
         </is>
       </c>
     </row>
@@ -1945,6 +2003,7 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1964,6 +2023,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1983,6 +2043,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -2002,6 +2063,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -2021,6 +2083,7 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -2040,6 +2103,7 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -2059,6 +2123,7 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -2078,6 +2143,7 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -2097,6 +2163,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -2116,6 +2183,7 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -2135,6 +2203,7 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -2154,6 +2223,7 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -2173,6 +2243,7 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2192,6 +2263,7 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2211,6 +2283,7 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2230,6 +2303,7 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2249,6 +2323,7 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2268,6 +2343,7 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2287,6 +2363,7 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2306,6 +2383,7 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2325,6 +2403,7 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2344,6 +2423,7 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2363,6 +2443,7 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2382,6 +2463,7 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2401,6 +2483,7 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2420,6 +2503,7 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2439,6 +2523,7 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2458,6 +2543,7 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2477,6 +2563,7 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2496,6 +2583,7 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2515,6 +2603,7 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
